--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487185_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487185_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. HUIZI ZUBELDIA</t>
+          <t>J. URTXULUTEGI NAVARRI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.524</v>
+        <v>0.3448</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7563</v>
+        <v>0.9937</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2323</v>
+        <v>-0.6489</v>
       </c>
       <c r="G2" t="n">
-        <v>-6.7784</v>
+        <v>-2.3901</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4822</v>
+        <v>-0.6107</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.2962</v>
+        <v>-1.7793</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.2997</v>
+        <v>0.2461</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9819</v>
+        <v>0.7916</v>
       </c>
       <c r="L2" t="n">
-        <v>-3.2816</v>
+        <v>-0.5455</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.4787</v>
+        <v>-2.6361</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.4641</v>
+        <v>-1.4023</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.0146</v>
+        <v>-1.2338</v>
       </c>
       <c r="P2" t="n">
-        <v>2.5091</v>
+        <v>1.7371</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.4741</v>
+        <v>1.7371</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3531</v>
+        <v>0.7119</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3372</v>
+        <v>0.1759</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0159</v>
+        <v>0.536</v>
       </c>
       <c r="V2" t="n">
-        <v>3.4403</v>
+        <v>0.2859</v>
       </c>
       <c r="W2" t="n">
-        <v>3.6839</v>
+        <v>0.5717</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2436</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. URTXULUTEGI NAVARRI</t>
+          <t>E. HUIZI ZUBELDIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2119</v>
+        <v>0.3426</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5931</v>
+        <v>1.8158</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3812</v>
+        <v>-1.4732</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.3901</v>
+        <v>-6.7784</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6107</v>
+        <v>-0.4822</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.7793</v>
+        <v>-6.2962</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2461</v>
+        <v>-1.2997</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7916</v>
+        <v>1.9819</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5455</v>
+        <v>-3.2816</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6361</v>
+        <v>-5.4787</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4023</v>
+        <v>-2.4641</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2338</v>
+        <v>-3.0146</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7371</v>
+        <v>2.5091</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7371</v>
+        <v>3.4741</v>
       </c>
       <c r="S3" t="n">
-        <v>0.579</v>
+        <v>1.1716</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2247</v>
+        <v>0.3966</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8037</v>
+        <v>0.775</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2859</v>
+        <v>3.4403</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5717</v>
+        <v>3.6839</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2859</v>
+        <v>-0.2436</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0457</v>
+        <v>-0.1786</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6152</v>
+        <v>4.2146</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.6609</v>
+        <v>-4.3932</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5308</v>
@@ -766,13 +766,13 @@
         <v>2.8951</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2295</v>
+        <v>1.0966</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0642</v>
+        <v>0.6637</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1652</v>
+        <v>0.4329</v>
       </c>
       <c r="V4" t="n">
         <v>1.1857</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6706</v>
+        <v>-0.5506</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9889</v>
+        <v>2.9483</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.6595</v>
+        <v>-3.4989</v>
       </c>
       <c r="G5" t="n">
         <v>3.3401</v>
@@ -844,13 +844,13 @@
         <v>2.3161</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5804</v>
+        <v>0.7003</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3834</v>
+        <v>0.3428</v>
       </c>
       <c r="U5" t="n">
-        <v>0.197</v>
+        <v>0.3576</v>
       </c>
       <c r="V5" t="n">
         <v>-4.012</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. ETXEBERRIA AGUIRREZABALA</t>
+          <t>U. CONDE LAKUNTZA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4028</v>
+        <v>-1.0231</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5334</v>
+        <v>-0.7195</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8694</v>
+        <v>-0.3036</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.4728</v>
+        <v>-2.0686</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2408</v>
+        <v>-0.8962</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.7136</v>
+        <v>-1.1724</v>
       </c>
       <c r="J6" t="n">
-        <v>1.424</v>
+        <v>1.1349</v>
       </c>
       <c r="K6" t="n">
-        <v>2.67</v>
+        <v>1.2006</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2459</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.8968</v>
+        <v>-3.2035</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4292</v>
+        <v>-2.0968</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.4677</v>
+        <v>-1.1067</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3511</v>
+        <v>-0.193</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2811</v>
+        <v>1.7371</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7033</v>
+        <v>0.5823</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.271</v>
+        <v>0.0757</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9843</v>
+        <v>0.6562</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2436</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.228</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>U. CONDE LAKUNTZA</t>
+          <t>B. ETXEBERRIA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5704</v>
+        <v>-1.257</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0794</v>
+        <v>-0.1735</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.491</v>
+        <v>-1.0836</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0686</v>
+        <v>-2.4728</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8962</v>
+        <v>1.2408</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1724</v>
+        <v>-3.7136</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1349</v>
+        <v>1.424</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2006</v>
+        <v>2.67</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-1.2459</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.2035</v>
+        <v>-3.8968</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.0968</v>
+        <v>-1.4292</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1067</v>
+        <v>-2.4677</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.193</v>
+        <v>1.3511</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7371</v>
+        <v>3.2811</v>
       </c>
       <c r="S7" t="n">
-        <v>0.035</v>
+        <v>0.849</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2842</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3192</v>
+        <v>0.7601</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6562</v>
+        <v>-0.9843</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2436</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6562</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9386</v>
+        <v>-1.999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4539</v>
+        <v>0.3131</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3925</v>
+        <v>-2.3122</v>
       </c>
       <c r="G8" t="n">
         <v>-2.754</v>
@@ -1078,13 +1078,13 @@
         <v>1.9301</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7502</v>
+        <v>0.6897</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5024</v>
+        <v>0.3616</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2479</v>
+        <v>0.3282</v>
       </c>
       <c r="V8" t="n">
         <v>-0.8999</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9614</v>
+        <v>-2.2351</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0569</v>
+        <v>-0.3573</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9046</v>
+        <v>-1.8778</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3594</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.626</v>
+        <v>0.3523</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5486</v>
+        <v>0.2482</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.1041</v>
       </c>
       <c r="V9" t="n">
         <v>-1.228</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.8536</v>
+        <v>-6.556</v>
       </c>
       <c r="E10" t="n">
-        <v>8.7377</v>
+        <v>9.0352</v>
       </c>
       <c r="F10" t="n">
         <v>-15.5914</v>
@@ -1234,10 +1234,10 @@
         <v>17.3707</v>
       </c>
       <c r="S10" t="n">
-        <v>5.8565</v>
+        <v>6.1537</v>
       </c>
       <c r="T10" t="n">
-        <v>2.0559</v>
+        <v>2.3534</v>
       </c>
       <c r="U10" t="n">
         <v>3.8005</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.7301</v>
+        <v>7.0166</v>
       </c>
       <c r="E11" t="n">
-        <v>7.9716</v>
+        <v>8.472300000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2415</v>
+        <v>-1.4557</v>
       </c>
       <c r="G11" t="n">
         <v>6.4563</v>
@@ -1312,13 +1312,13 @@
         <v>1.7371</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.047</v>
+        <v>-0.7605</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9518</v>
+        <v>-0.4511</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.3094</v>
       </c>
       <c r="V11" t="n">
         <v>1.5138</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.4408</v>
+        <v>5.1091</v>
       </c>
       <c r="E12" t="n">
-        <v>5.7549</v>
+        <v>6.1555</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3141</v>
+        <v>-1.0464</v>
       </c>
       <c r="G12" t="n">
         <v>2.7452</v>
@@ -1390,13 +1390,13 @@
         <v>1.5441</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6022</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8328</v>
+        <v>-0.4323</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7694</v>
+        <v>-0.5017</v>
       </c>
       <c r="V12" t="n">
         <v>3.6839</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7284</v>
+        <v>2.8322</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4257</v>
+        <v>3.2255</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3027</v>
+        <v>-0.3933</v>
       </c>
       <c r="G13" t="n">
         <v>4.2667</v>
@@ -1468,13 +1468,13 @@
         <v>1.9301</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1639</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4032</v>
+        <v>-0.6035</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5671</v>
+        <v>-0.1289</v>
       </c>
       <c r="V13" t="n">
         <v>1.228</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9105</v>
+        <v>1.1306</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5553</v>
+        <v>1.8557</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6447000000000001</v>
+        <v>-0.725</v>
       </c>
       <c r="G14" t="n">
         <v>0.9076</v>
@@ -1546,13 +1546,13 @@
         <v>0.965</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6762</v>
+        <v>-0.4561</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7139</v>
+        <v>-0.4134</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0377</v>
+        <v>-0.0427</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2859</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.149</v>
+        <v>0.3562</v>
       </c>
       <c r="E15" t="n">
-        <v>1.75</v>
+        <v>1.8501</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.601</v>
+        <v>-1.4939</v>
       </c>
       <c r="G15" t="n">
         <v>2.2125</v>
@@ -1624,13 +1624,13 @@
         <v>1.158</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0708</v>
+        <v>-0.8636</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8923</v>
+        <v>-0.7922</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1785</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-1.1857</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6881</v>
+        <v>-0.4541</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6415</v>
+        <v>-0.5414</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0466</v>
+        <v>0.0872</v>
       </c>
       <c r="G16" t="n">
         <v>0.1731</v>
@@ -1702,13 +1702,13 @@
         <v>0.579</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4752</v>
+        <v>-0.2413</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3569</v>
+        <v>-0.2568</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1183</v>
+        <v>0.0155</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9208</v>
+        <v>-0.7938</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8442</v>
+        <v>-0.744</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0766</v>
+        <v>-0.0498</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9530999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>0.386</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3536</v>
+        <v>-0.2267</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.238</v>
+        <v>-0.1378</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1157</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8562</v>
+        <v>-1.6956</v>
       </c>
       <c r="E18" t="n">
         <v>-0.6511</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2051</v>
+        <v>-1.0445</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5629</v>
@@ -1858,13 +1858,13 @@
         <v>1.9301</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0497</v>
+        <v>-0.889</v>
       </c>
       <c r="T18" t="n">
         <v>-0.7139</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3358</v>
+        <v>-0.1752</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2436</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.276</v>
+        <v>-3.2437</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2651</v>
+        <v>-1.3666</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.011</v>
+        <v>-1.8771</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6826</v>
@@ -1936,13 +1936,13 @@
         <v>1.5441</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0821</v>
+        <v>0.1144</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5269</v>
+        <v>0.4254</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4449</v>
+        <v>-0.311</v>
       </c>
       <c r="V19" t="n">
         <v>-2.2546</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3642</v>
+        <v>-3.4039</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4644</v>
+        <v>-2.6646</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8999</v>
+        <v>-0.7392</v>
       </c>
       <c r="G20" t="n">
         <v>1.4513</v>
@@ -2014,13 +2014,13 @@
         <v>1.7371</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8276</v>
+        <v>-0.8672</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2247</v>
+        <v>-0.425</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6029</v>
+        <v>-0.4422</v>
       </c>
       <c r="V20" t="n">
         <v>-0.8999</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>6.853499999999999</v>
+        <v>6.8536</v>
       </c>
       <c r="E21" t="n">
-        <v>15.5912</v>
+        <v>15.5914</v>
       </c>
       <c r="F21" t="n">
-        <v>-8.7378</v>
+        <v>-8.7377</v>
       </c>
       <c r="G21" t="n">
         <v>15.0141</v>
@@ -2092,7 +2092,7 @@
         <v>13.5106</v>
       </c>
       <c r="S21" t="n">
-        <v>-5.856300000000001</v>
+        <v>-5.856400000000001</v>
       </c>
       <c r="T21" t="n">
         <v>-3.8006</v>
